--- a/marketing_report/outputs/Cursos/Matcheo_Completo/Con_Duplicados_Cursos.xlsx
+++ b/marketing_report/outputs/Cursos/Matcheo_Completo/Con_Duplicados_Cursos.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="507">
   <si>
     <t>Consulta: ID Consulta</t>
   </si>
@@ -376,18 +376,6 @@
     <t>003TV0000059z31YAA</t>
   </si>
   <si>
-    <t>00QTV00000Vepl72AB</t>
-  </si>
-  <si>
-    <t>00QTV00000TdRUI2A3</t>
-  </si>
-  <si>
-    <t>00QTV00000RBIN42AP</t>
-  </si>
-  <si>
-    <t>00QTV00000RgMLC2A3</t>
-  </si>
-  <si>
     <t>003TV00000FLbznYAD</t>
   </si>
   <si>
@@ -403,6 +391,9 @@
     <t>00QTV00000VPpiE2AT</t>
   </si>
   <si>
+    <t>00QTV00000Tqli62AB</t>
+  </si>
+  <si>
     <t>00QTV00000Haz4q2AB</t>
   </si>
   <si>
@@ -451,18 +442,6 @@
     <t>victoriadohrman@gmail.com</t>
   </si>
   <si>
-    <t>roxanaojeda_berisso@hotmail.com</t>
-  </si>
-  <si>
-    <t>giselagarrone03@gmail.com</t>
-  </si>
-  <si>
-    <t>verorescobar@hotmail.com</t>
-  </si>
-  <si>
-    <t>azullonghi@gmail.com</t>
-  </si>
-  <si>
     <t>antonellacarlamartinez2001@gmail.com</t>
   </si>
   <si>
@@ -478,6 +457,9 @@
     <t>gmlun2@gmail.com</t>
   </si>
   <si>
+    <t>melilagoria@gmail.com</t>
+  </si>
+  <si>
     <t>marihenderson@hotmail.com.ar</t>
   </si>
   <si>
@@ -535,18 +517,6 @@
     <t>Victoria</t>
   </si>
   <si>
-    <t>Roxana Ojeda</t>
-  </si>
-  <si>
-    <t>Gisela Garrone</t>
-  </si>
-  <si>
-    <t>Veronica Escobar</t>
-  </si>
-  <si>
-    <t>&amp;deg;Azul&amp;deg;</t>
-  </si>
-  <si>
     <t>Antonella Martinez</t>
   </si>
   <si>
@@ -562,6 +532,9 @@
     <t>Maxi Luna</t>
   </si>
   <si>
+    <t>Melina Lagoria</t>
+  </si>
+  <si>
     <t>Mariela Mariela</t>
   </si>
   <si>
@@ -664,33 +637,33 @@
     <t>TECNICATURA EN OPERACIONES MINERAS E INDUSTRIALES</t>
   </si>
   <si>
-    <t>LICENCIATURA EN CRIMINOLOGÍA</t>
+    <t>PROFESORADO EN  EDUCACIÓN FÍSICA</t>
+  </si>
+  <si>
+    <t>LICENCIATURA EN GESTIÓN EDUCATIVA - CICLO DE LICENCIATURA</t>
+  </si>
+  <si>
+    <t>LICENCIATURA EN LENGUAJES EXPRESIVOS - CICLO DE COMPLEMENTACIÓN CURRICULAR</t>
+  </si>
+  <si>
+    <t>FORMACION DOCENTE PARA PROFESIONALES</t>
+  </si>
+  <si>
+    <t>LICENCIATURA EN RECREACIÓN Y OCIO EDUCATIVO - CICLO DE COMPLEMENTACIÓN CURRIC...</t>
   </si>
   <si>
     <t>INGRESO A LIC. EN TERAPIA OCUPACIONAL</t>
   </si>
   <si>
-    <t>PROFESORADO EN  EDUCACIÓN FÍSICA</t>
-  </si>
-  <si>
-    <t>LICENCIATURA EN GESTIÓN EDUCATIVA - CICLO DE LICENCIATURA</t>
-  </si>
-  <si>
-    <t>LICENCIATURA EN LENGUAJES EXPRESIVOS - CICLO DE COMPLEMENTACIÓN CURRICULAR</t>
-  </si>
-  <si>
-    <t>FORMACION DOCENTE PARA PROFESIONALES</t>
-  </si>
-  <si>
-    <t>LICENCIATURA EN RECREACIÓN Y OCIO EDUCATIVO - CICLO DE COMPLEMENTACIÓN CURRIC...</t>
-  </si>
-  <si>
     <t>ARQUITECTURA</t>
   </si>
   <si>
     <t>LICENCIATURA EN ENTRENAMIENTO DEPORTIVO - CICLO DE COMPLEMENTACIÓN CURRICULAR</t>
   </si>
   <si>
+    <t>LICENCIATURA EN RECURSOS HUMANOS</t>
+  </si>
+  <si>
     <t>TECNICATURA UNIVERSITARIA EN ORGANIZACIÓN Y DIRECCIÓN DE EVENTOS Y CEREMONIAL</t>
   </si>
   <si>
@@ -856,18 +829,6 @@
     <t>2025-10-28 00:00:00</t>
   </si>
   <si>
-    <t>26/2/2026</t>
-  </si>
-  <si>
-    <t>3/1/2026</t>
-  </si>
-  <si>
-    <t>2025-11-02 00:00:00</t>
-  </si>
-  <si>
-    <t>2025-11-12 00:00:00</t>
-  </si>
-  <si>
     <t>18/2/2026</t>
   </si>
   <si>
@@ -892,6 +853,9 @@
     <t>19/2/2026</t>
   </si>
   <si>
+    <t>8/1/2026</t>
+  </si>
+  <si>
     <t>23/3/2025</t>
   </si>
   <si>
@@ -904,15 +868,15 @@
     <t>3.Frío</t>
   </si>
   <si>
-    <t>7/1/2026, 04:02</t>
-  </si>
-  <si>
     <t>19/2/2026, 14:02</t>
   </si>
   <si>
     <t>23/2/2026, 22:03</t>
   </si>
   <si>
+    <t>9/1/2026, 00:01</t>
+  </si>
+  <si>
     <t>UCASAL Prod</t>
   </si>
   <si>
@@ -937,12 +901,6 @@
     <t>Victoria Dohrman</t>
   </si>
   <si>
-    <t>Veronica Escobar N/D</t>
-  </si>
-  <si>
-    <t>&amp;deg;Azul&amp;deg; N/D</t>
-  </si>
-  <si>
     <t>Belu&amp;lowbar;Davalos N/D</t>
   </si>
   <si>
@@ -976,6 +934,9 @@
     <t>Jorge Ariel Cabaña</t>
   </si>
   <si>
+    <t>Estefanía Pamela Quintana</t>
+  </si>
+  <si>
     <t>Daniel Luciano Chaile Soto</t>
   </si>
   <si>
@@ -1072,24 +1033,24 @@
     <t>48338981</t>
   </si>
   <si>
+    <t>43218927</t>
+  </si>
+  <si>
+    <t>31610846</t>
+  </si>
+  <si>
+    <t>45018481</t>
+  </si>
+  <si>
+    <t>42917340</t>
+  </si>
+  <si>
+    <t>23850969</t>
+  </si>
+  <si>
     <t>43218584</t>
   </si>
   <si>
-    <t>43218927</t>
-  </si>
-  <si>
-    <t>31610846</t>
-  </si>
-  <si>
-    <t>45018481</t>
-  </si>
-  <si>
-    <t>42917340</t>
-  </si>
-  <si>
-    <t>23850969</t>
-  </si>
-  <si>
     <t>23012881</t>
   </si>
   <si>
@@ -1138,24 +1099,24 @@
     <t>DOHRMAN, VICTORIA</t>
   </si>
   <si>
+    <t xml:space="preserve">MARTINEZ , CARLA ANTONELLA </t>
+  </si>
+  <si>
+    <t>BURGOS , NADIA LIS</t>
+  </si>
+  <si>
+    <t>MORA DAVALOS, MARÍA BELÉN</t>
+  </si>
+  <si>
+    <t>VELES, ELISA MARIA FLORENCIA</t>
+  </si>
+  <si>
+    <t>LUNA, PABLO FEDERICO MOISÉS</t>
+  </si>
+  <si>
     <t>GIMENEZ LAGORIA , MARIA MICAELA</t>
   </si>
   <si>
-    <t xml:space="preserve">MARTINEZ , CARLA ANTONELLA </t>
-  </si>
-  <si>
-    <t>BURGOS , NADIA LIS</t>
-  </si>
-  <si>
-    <t>MORA DAVALOS, MARÍA BELÉN</t>
-  </si>
-  <si>
-    <t>VELES, ELISA MARIA FLORENCIA</t>
-  </si>
-  <si>
-    <t>LUNA, PABLO FEDERICO MOISÉS</t>
-  </si>
-  <si>
     <t>CAPALDO, MARIELA ELSA</t>
   </si>
   <si>
@@ -1174,24 +1135,24 @@
     <t>yazmincabrerizo@gmail.com</t>
   </si>
   <si>
+    <t>Martinezcarla981antonella@gmail.com</t>
+  </si>
+  <si>
+    <t>lisburgos@gmail.com</t>
+  </si>
+  <si>
+    <t>belendavalos07@gmail.com</t>
+  </si>
+  <si>
+    <t>elisita_veles@hotmail.com</t>
+  </si>
+  <si>
+    <t>pmluna@gmail.com</t>
+  </si>
+  <si>
     <t>marilagoria@gmail.com</t>
   </si>
   <si>
-    <t>Martinezcarla981antonella@gmail.com</t>
-  </si>
-  <si>
-    <t>lisburgos@gmail.com</t>
-  </si>
-  <si>
-    <t>belendavalos07@gmail.com</t>
-  </si>
-  <si>
-    <t>elisita_veles@hotmail.com</t>
-  </si>
-  <si>
-    <t>pmluna@gmail.com</t>
-  </si>
-  <si>
     <t>marielacapaldo@gmail.com</t>
   </si>
   <si>
@@ -1228,24 +1189,24 @@
     <t>387 - 4851679</t>
   </si>
   <si>
+    <t>387 - 5832169</t>
+  </si>
+  <si>
+    <t>3885 - 080215</t>
+  </si>
+  <si>
+    <t>387 - 5016891</t>
+  </si>
+  <si>
+    <t>387 - 4260918</t>
+  </si>
+  <si>
+    <t>387 - 4206212</t>
+  </si>
+  <si>
     <t>0 - 0000</t>
   </si>
   <si>
-    <t>387 - 5832169</t>
-  </si>
-  <si>
-    <t>3885 - 080215</t>
-  </si>
-  <si>
-    <t>387 - 5016891</t>
-  </si>
-  <si>
-    <t>387 - 4260918</t>
-  </si>
-  <si>
-    <t>387 - 4206212</t>
-  </si>
-  <si>
     <t>387 - 5298537</t>
   </si>
   <si>
@@ -1273,15 +1234,15 @@
     <t>-3874851679</t>
   </si>
   <si>
+    <t>387 - 5016886</t>
+  </si>
+  <si>
+    <t>387 - 2132387</t>
+  </si>
+  <si>
     <t>387 - 4624817</t>
   </si>
   <si>
-    <t>387 - 5016886</t>
-  </si>
-  <si>
-    <t>387 - 2132387</t>
-  </si>
-  <si>
     <t>387 - 5607351</t>
   </si>
   <si>
@@ -1420,21 +1381,21 @@
     <t>8-1957388,18436846</t>
   </si>
   <si>
+    <t>9-2232767,18447451</t>
+  </si>
+  <si>
+    <t>9-2224390,18403372</t>
+  </si>
+  <si>
+    <t>8-1958612,0</t>
+  </si>
+  <si>
+    <t>9-2241945,18501853</t>
+  </si>
+  <si>
     <t>8-1961356,0</t>
   </si>
   <si>
-    <t>9-2232767,18447451</t>
-  </si>
-  <si>
-    <t>9-2224390,18403372</t>
-  </si>
-  <si>
-    <t>8-1958612,0</t>
-  </si>
-  <si>
-    <t>9-2241945,18501853</t>
-  </si>
-  <si>
     <t>8-1969009,0</t>
   </si>
   <si>
@@ -1483,24 +1444,24 @@
     <t>DOHRMAN</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>BURGOS</t>
+  </si>
+  <si>
+    <t>MORA DAVALOS</t>
+  </si>
+  <si>
+    <t>VELES</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>GIMENEZ LAGORIA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>BURGOS</t>
-  </si>
-  <si>
-    <t>MORA DAVALOS</t>
-  </si>
-  <si>
-    <t>VELES</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
     <t>CAPALDO</t>
   </si>
   <si>
@@ -1531,22 +1492,22 @@
     <t>VICTORIA</t>
   </si>
   <si>
+    <t>CARLA ANTONELLA</t>
+  </si>
+  <si>
+    <t>NADIA LIS</t>
+  </si>
+  <si>
+    <t>MARÍA BELÉN</t>
+  </si>
+  <si>
+    <t>ELISA MARIA FLORENCIA</t>
+  </si>
+  <si>
+    <t>PABLO FEDERICO MOISÉS</t>
+  </si>
+  <si>
     <t>MARIA MICAELA</t>
-  </si>
-  <si>
-    <t>CARLA ANTONELLA</t>
-  </si>
-  <si>
-    <t>NADIA LIS</t>
-  </si>
-  <si>
-    <t>MARÍA BELÉN</t>
-  </si>
-  <si>
-    <t>ELISA MARIA FLORENCIA</t>
-  </si>
-  <si>
-    <t>PABLO FEDERICO MOISÉS</t>
   </si>
   <si>
     <t>MARIELA ELSA</t>
@@ -1940,7 +1901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DE45"/>
+  <dimension ref="A1:DE42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -2386,103 +2347,103 @@
         <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E2" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F2">
         <v>54902266661904</v>
       </c>
       <c r="H2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="M2">
         <v>3</v>
       </c>
       <c r="S2" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="T2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="U2" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="V2" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="W2" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="Y2" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="AA2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="BB2">
         <v>148</v>
       </c>
       <c r="BC2" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="BD2">
         <v>9</v>
       </c>
       <c r="BE2" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="BF2">
         <v>1013</v>
       </c>
       <c r="BG2" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="BH2">
         <v>7</v>
       </c>
       <c r="BI2" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="BJ2" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK2" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL2" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="BM2" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="BN2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BO2" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="BP2" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="BQ2">
         <v>11</v>
       </c>
       <c r="BV2" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="BW2">
         <v>75000</v>
       </c>
       <c r="BX2" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="BY2" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="BZ2">
         <v>2026</v>
@@ -2491,19 +2452,19 @@
         <v>50</v>
       </c>
       <c r="CB2" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="CC2" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="CD2" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="CE2" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE2" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3" spans="1:109">
@@ -2514,61 +2475,61 @@
         <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F3">
         <v>5493874489311</v>
       </c>
       <c r="G3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H3" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I3">
         <v>123</v>
       </c>
       <c r="J3" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M3">
         <v>3</v>
       </c>
       <c r="S3" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="T3" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="U3" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="V3" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="W3" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="Y3" t="s">
+        <v>286</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AC3" t="s">
         <v>298</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>312</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -2577,46 +2538,46 @@
         <v>1</v>
       </c>
       <c r="BC3" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD3">
         <v>9</v>
       </c>
       <c r="BE3" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="BF3">
         <v>1644</v>
       </c>
       <c r="BG3" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="BH3">
         <v>1</v>
       </c>
       <c r="BI3" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ3" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK3" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="BM3" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="BN3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="BO3" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="BP3" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="BQ3">
         <v>1</v>
@@ -2625,25 +2586,25 @@
         <v>2</v>
       </c>
       <c r="BS3" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="BT3">
         <v>2491</v>
       </c>
       <c r="BU3" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="BV3" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="BW3">
         <v>175000</v>
       </c>
       <c r="BX3" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY3" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ3">
         <v>2026</v>
@@ -2652,19 +2613,19 @@
         <v>50</v>
       </c>
       <c r="CB3" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="CC3" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="CD3" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="CE3" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE3" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" spans="1:109">
@@ -2675,100 +2636,100 @@
         <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F4">
         <v>3704520570</v>
       </c>
       <c r="G4" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H4" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I4">
         <v>221</v>
       </c>
       <c r="J4" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="T4" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="U4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="V4" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="W4" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="Y4" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="Z4" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="AA4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="BB4">
         <v>1</v>
       </c>
       <c r="BC4" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD4">
         <v>24</v>
       </c>
       <c r="BE4" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF4">
         <v>964</v>
       </c>
       <c r="BG4" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="BH4">
         <v>1</v>
       </c>
       <c r="BI4" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ4" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK4" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL4" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="BM4" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="BN4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="BO4" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="BP4" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="BQ4">
         <v>1</v>
@@ -2777,25 +2738,25 @@
         <v>3</v>
       </c>
       <c r="BS4" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT4">
         <v>10</v>
       </c>
       <c r="BU4" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="BV4" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="BW4">
         <v>90300</v>
       </c>
       <c r="BX4" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY4" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ4">
         <v>2026</v>
@@ -2804,19 +2765,19 @@
         <v>50</v>
       </c>
       <c r="CB4" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="CC4" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="CD4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="CE4" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE4" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="5" spans="1:109">
@@ -2827,100 +2788,100 @@
         <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E5" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F5">
         <v>3704520570</v>
       </c>
       <c r="G5" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H5" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I5">
         <v>221</v>
       </c>
       <c r="J5" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="T5" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="U5" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="V5" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="W5" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="Y5" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="Z5" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="AA5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="BB5">
         <v>1</v>
       </c>
       <c r="BC5" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD5">
         <v>24</v>
       </c>
       <c r="BE5" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF5">
         <v>965</v>
       </c>
       <c r="BG5" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="BH5">
         <v>1</v>
       </c>
       <c r="BI5" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ5" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK5" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL5" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="BM5" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="BN5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="BO5" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="BP5" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="BQ5">
         <v>1</v>
@@ -2929,25 +2890,25 @@
         <v>3</v>
       </c>
       <c r="BS5" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT5">
         <v>10</v>
       </c>
       <c r="BU5" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="BV5" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="BW5">
         <v>90300</v>
       </c>
       <c r="BX5" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY5" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ5">
         <v>2026</v>
@@ -2956,19 +2917,19 @@
         <v>50</v>
       </c>
       <c r="CB5" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="CC5" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="CD5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="CE5" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE5" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" spans="1:109">
@@ -2979,97 +2940,97 @@
         <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D6" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E6" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F6">
         <v>3704520570</v>
       </c>
       <c r="G6" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I6">
         <v>222</v>
       </c>
       <c r="J6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="T6" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="U6" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="V6" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="W6" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="Y6" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="AA6" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="BB6">
         <v>1</v>
       </c>
       <c r="BC6" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD6">
         <v>24</v>
       </c>
       <c r="BE6" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF6">
         <v>964</v>
       </c>
       <c r="BG6" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="BH6">
         <v>1</v>
       </c>
       <c r="BI6" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ6" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK6" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL6" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="BM6" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="BN6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="BO6" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="BP6" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="BQ6">
         <v>1</v>
@@ -3078,25 +3039,25 @@
         <v>3</v>
       </c>
       <c r="BS6" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT6">
         <v>10</v>
       </c>
       <c r="BU6" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="BV6" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="BW6">
         <v>90300</v>
       </c>
       <c r="BX6" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY6" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ6">
         <v>2026</v>
@@ -3105,19 +3066,19 @@
         <v>50</v>
       </c>
       <c r="CB6" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="CC6" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="CD6" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="CE6" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE6" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7" spans="1:109">
@@ -3128,97 +3089,97 @@
         <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E7" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F7">
         <v>3704520570</v>
       </c>
       <c r="G7" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H7" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I7">
         <v>222</v>
       </c>
       <c r="J7" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="T7" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="U7" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="V7" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="W7" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="Y7" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="AA7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="BB7">
         <v>1</v>
       </c>
       <c r="BC7" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD7">
         <v>24</v>
       </c>
       <c r="BE7" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF7">
         <v>965</v>
       </c>
       <c r="BG7" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="BH7">
         <v>1</v>
       </c>
       <c r="BI7" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ7" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK7" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL7" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="BM7" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="BN7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="BO7" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="BP7" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="BQ7">
         <v>1</v>
@@ -3227,25 +3188,25 @@
         <v>3</v>
       </c>
       <c r="BS7" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT7">
         <v>10</v>
       </c>
       <c r="BU7" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="BV7" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="BW7">
         <v>90300</v>
       </c>
       <c r="BX7" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY7" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ7">
         <v>2026</v>
@@ -3254,19 +3215,19 @@
         <v>50</v>
       </c>
       <c r="CB7" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="CC7" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="CD7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="CE7" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE7" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8" spans="1:109">
@@ -3277,100 +3238,100 @@
         <v>112</v>
       </c>
       <c r="C8" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E8" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F8">
         <v>54903885087117</v>
       </c>
       <c r="G8" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H8" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I8">
         <v>175</v>
       </c>
       <c r="J8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="K8">
         <v>10</v>
       </c>
       <c r="L8" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="M8">
         <v>3</v>
       </c>
       <c r="T8" t="s">
+        <v>247</v>
+      </c>
+      <c r="U8" t="s">
+        <v>250</v>
+      </c>
+      <c r="V8" t="s">
         <v>256</v>
       </c>
-      <c r="U8" t="s">
-        <v>259</v>
-      </c>
-      <c r="V8" t="s">
-        <v>265</v>
-      </c>
       <c r="W8" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="Y8" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="AA8" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="BB8">
         <v>1</v>
       </c>
       <c r="BC8" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD8">
         <v>24</v>
       </c>
       <c r="BE8" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF8">
         <v>965</v>
       </c>
       <c r="BG8" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="BH8">
         <v>1</v>
       </c>
       <c r="BI8" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ8" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK8" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL8" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="BM8" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="BN8" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="BO8" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BP8" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BQ8">
         <v>1</v>
@@ -3379,40 +3340,40 @@
         <v>3</v>
       </c>
       <c r="BS8" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT8">
         <v>1110</v>
       </c>
       <c r="BU8" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="BV8" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="BW8">
         <v>56500</v>
       </c>
       <c r="BX8" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY8" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ8">
         <v>2026</v>
       </c>
       <c r="CC8" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="CD8" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="CE8" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE8" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9" spans="1:109">
@@ -3423,100 +3384,100 @@
         <v>112</v>
       </c>
       <c r="C9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F9">
         <v>54903885087117</v>
       </c>
       <c r="G9" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H9" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I9">
         <v>175</v>
       </c>
       <c r="J9" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="K9">
         <v>28</v>
       </c>
       <c r="L9" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="M9">
         <v>103</v>
       </c>
       <c r="T9" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="U9" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="V9" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="W9" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="Y9" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="AA9" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="BB9">
         <v>1</v>
       </c>
       <c r="BC9" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD9">
         <v>24</v>
       </c>
       <c r="BE9" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF9">
         <v>965</v>
       </c>
       <c r="BG9" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="BH9">
         <v>1</v>
       </c>
       <c r="BI9" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ9" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK9" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL9" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="BM9" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="BN9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="BO9" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BP9" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BQ9">
         <v>1</v>
@@ -3525,40 +3486,40 @@
         <v>3</v>
       </c>
       <c r="BS9" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT9">
         <v>1110</v>
       </c>
       <c r="BU9" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="BV9" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="BW9">
         <v>56500</v>
       </c>
       <c r="BX9" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY9" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ9">
         <v>2026</v>
       </c>
       <c r="CC9" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="CD9" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="CE9" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE9" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="10" spans="1:109">
@@ -3569,100 +3530,100 @@
         <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E10" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F10">
         <v>5493885087117</v>
       </c>
       <c r="G10" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H10" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I10">
         <v>175</v>
       </c>
       <c r="J10" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="K10">
         <v>28</v>
       </c>
       <c r="L10" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="M10">
         <v>3</v>
       </c>
       <c r="T10" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="U10" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="V10" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="W10" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="Y10" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="AA10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="BB10">
         <v>1</v>
       </c>
       <c r="BC10" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD10">
         <v>24</v>
       </c>
       <c r="BE10" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF10">
         <v>965</v>
       </c>
       <c r="BG10" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="BH10">
         <v>1</v>
       </c>
       <c r="BI10" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ10" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK10" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL10" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="BM10" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="BN10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="BO10" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BP10" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BQ10">
         <v>1</v>
@@ -3671,40 +3632,40 @@
         <v>3</v>
       </c>
       <c r="BS10" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT10">
         <v>1110</v>
       </c>
       <c r="BU10" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="BV10" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="BW10">
         <v>56500</v>
       </c>
       <c r="BX10" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY10" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ10">
         <v>2026</v>
       </c>
       <c r="CC10" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="CD10" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="CE10" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE10" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" spans="1:109">
@@ -3712,49 +3673,49 @@
         <v>1523322</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F11">
         <v>543885087117</v>
       </c>
       <c r="G11" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H11" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I11">
         <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="K11">
         <v>10</v>
       </c>
       <c r="L11" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="M11">
         <v>18</v>
       </c>
       <c r="S11" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="U11" t="s">
+        <v>249</v>
+      </c>
+      <c r="V11" t="s">
         <v>258</v>
       </c>
-      <c r="V11" t="s">
-        <v>267</v>
-      </c>
       <c r="AC11" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AD11">
         <v>1</v>
@@ -3763,46 +3724,46 @@
         <v>1</v>
       </c>
       <c r="BC11" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD11">
         <v>24</v>
       </c>
       <c r="BE11" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF11">
         <v>965</v>
       </c>
       <c r="BG11" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="BH11">
         <v>1</v>
       </c>
       <c r="BI11" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ11" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK11" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL11" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="BM11" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="BN11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="BO11" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BP11" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BQ11">
         <v>1</v>
@@ -3811,40 +3772,40 @@
         <v>3</v>
       </c>
       <c r="BS11" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT11">
         <v>1110</v>
       </c>
       <c r="BU11" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="BV11" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="BW11">
         <v>56500</v>
       </c>
       <c r="BX11" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY11" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ11">
         <v>2026</v>
       </c>
       <c r="CC11" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="CD11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="CE11" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE11" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="12" spans="1:109">
@@ -3852,49 +3813,49 @@
         <v>1537201</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D12" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F12">
         <v>5493885087117</v>
       </c>
       <c r="G12" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H12" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I12">
         <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="K12">
         <v>10</v>
       </c>
       <c r="L12" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="M12">
         <v>4</v>
       </c>
       <c r="S12" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="U12" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="V12" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="AC12" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AD12">
         <v>1</v>
@@ -3903,46 +3864,46 @@
         <v>1</v>
       </c>
       <c r="BC12" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD12">
         <v>24</v>
       </c>
       <c r="BE12" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF12">
         <v>965</v>
       </c>
       <c r="BG12" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="BH12">
         <v>1</v>
       </c>
       <c r="BI12" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ12" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK12" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL12" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="BM12" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="BN12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="BO12" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BP12" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BQ12">
         <v>1</v>
@@ -3951,40 +3912,40 @@
         <v>3</v>
       </c>
       <c r="BS12" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT12">
         <v>1110</v>
       </c>
       <c r="BU12" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="BV12" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="BW12">
         <v>56500</v>
       </c>
       <c r="BX12" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY12" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ12">
         <v>2026</v>
       </c>
       <c r="CC12" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="CD12" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="CE12" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE12" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="13" spans="1:109">
@@ -3992,49 +3953,49 @@
         <v>1538020</v>
       </c>
       <c r="C13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D13" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E13" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F13">
         <v>5493885087117</v>
       </c>
       <c r="G13" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H13" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I13">
         <v>17</v>
       </c>
       <c r="J13" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="K13">
         <v>10</v>
       </c>
       <c r="L13" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="M13">
         <v>3</v>
       </c>
       <c r="S13" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="U13" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="V13" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="AC13" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AD13">
         <v>1</v>
@@ -4043,46 +4004,46 @@
         <v>1</v>
       </c>
       <c r="BC13" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD13">
         <v>24</v>
       </c>
       <c r="BE13" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF13">
         <v>965</v>
       </c>
       <c r="BG13" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="BH13">
         <v>1</v>
       </c>
       <c r="BI13" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ13" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK13" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL13" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="BM13" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="BN13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="BO13" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BP13" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BQ13">
         <v>1</v>
@@ -4091,40 +4052,40 @@
         <v>3</v>
       </c>
       <c r="BS13" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT13">
         <v>1110</v>
       </c>
       <c r="BU13" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="BV13" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="BW13">
         <v>56500</v>
       </c>
       <c r="BX13" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY13" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ13">
         <v>2026</v>
       </c>
       <c r="CC13" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="CD13" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="CE13" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE13" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14" spans="1:109">
@@ -4132,49 +4093,49 @@
         <v>1545282</v>
       </c>
       <c r="C14" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E14" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F14">
         <v>3885087117</v>
       </c>
       <c r="G14" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H14" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I14">
         <v>86</v>
       </c>
       <c r="J14" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M14">
         <v>3</v>
       </c>
       <c r="S14" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="U14" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="V14" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="AC14" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -4183,46 +4144,46 @@
         <v>1</v>
       </c>
       <c r="BC14" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD14">
         <v>24</v>
       </c>
       <c r="BE14" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF14">
         <v>965</v>
       </c>
       <c r="BG14" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="BH14">
         <v>1</v>
       </c>
       <c r="BI14" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ14" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK14" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL14" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="BM14" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="BN14" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="BO14" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BP14" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BQ14">
         <v>1</v>
@@ -4231,40 +4192,40 @@
         <v>3</v>
       </c>
       <c r="BS14" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT14">
         <v>1110</v>
       </c>
       <c r="BU14" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="BV14" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="BW14">
         <v>56500</v>
       </c>
       <c r="BX14" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY14" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ14">
         <v>2026</v>
       </c>
       <c r="CC14" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="CD14" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="CE14" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE14" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="15" spans="1:109">
@@ -4272,49 +4233,49 @@
         <v>1538022</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E15" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F15">
         <v>3885087117</v>
       </c>
       <c r="G15" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H15" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I15">
         <v>86</v>
       </c>
       <c r="J15" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="K15">
         <v>10</v>
       </c>
       <c r="L15" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="M15">
         <v>3</v>
       </c>
       <c r="S15" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="U15" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="V15" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="AC15" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -4323,46 +4284,46 @@
         <v>1</v>
       </c>
       <c r="BC15" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD15">
         <v>24</v>
       </c>
       <c r="BE15" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF15">
         <v>965</v>
       </c>
       <c r="BG15" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="BH15">
         <v>1</v>
       </c>
       <c r="BI15" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ15" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK15" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL15" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="BM15" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="BN15" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="BO15" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BP15" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="BQ15">
         <v>1</v>
@@ -4371,40 +4332,40 @@
         <v>3</v>
       </c>
       <c r="BS15" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT15">
         <v>1110</v>
       </c>
       <c r="BU15" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="BV15" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="BW15">
         <v>56500</v>
       </c>
       <c r="BX15" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY15" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ15">
         <v>2026</v>
       </c>
       <c r="CC15" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="CD15" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="CE15" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE15" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="16" spans="1:109">
@@ -4415,64 +4376,64 @@
         <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D16" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E16" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F16">
         <v>543875182052</v>
       </c>
       <c r="G16" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H16" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I16">
         <v>214</v>
       </c>
       <c r="J16" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M16">
         <v>4</v>
       </c>
       <c r="N16" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="O16" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="P16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="Q16" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="R16">
         <v>619288243159</v>
       </c>
       <c r="U16" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="V16" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AA16" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="AC16" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -4481,46 +4442,46 @@
         <v>1</v>
       </c>
       <c r="BC16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD16">
         <v>24</v>
       </c>
       <c r="BE16" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF16">
         <v>1594</v>
       </c>
       <c r="BG16" t="s">
+        <v>318</v>
+      </c>
+      <c r="BH16">
+        <v>1</v>
+      </c>
+      <c r="BI16" t="s">
         <v>331</v>
       </c>
-      <c r="BH16">
-        <v>1</v>
-      </c>
-      <c r="BI16" t="s">
-        <v>344</v>
-      </c>
       <c r="BJ16" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK16" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL16" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="BM16" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="BN16" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="BO16" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="BP16" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="BQ16">
         <v>1</v>
@@ -4529,25 +4490,25 @@
         <v>3</v>
       </c>
       <c r="BS16" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT16">
         <v>2190</v>
       </c>
       <c r="BU16" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="BV16" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="BW16">
         <v>90300</v>
       </c>
       <c r="BX16" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY16" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ16">
         <v>2026</v>
@@ -4556,19 +4517,19 @@
         <v>50</v>
       </c>
       <c r="CB16" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="CC16" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="CD16" t="s">
+        <v>486</v>
+      </c>
+      <c r="CE16" t="s">
         <v>499</v>
       </c>
-      <c r="CE16" t="s">
-        <v>512</v>
-      </c>
       <c r="DE16" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="17" spans="1:109">
@@ -4579,67 +4540,67 @@
         <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E17" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="F17">
         <v>543813007337</v>
       </c>
       <c r="G17" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H17" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I17">
         <v>231</v>
       </c>
       <c r="J17" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M17">
         <v>130</v>
       </c>
       <c r="N17" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="O17" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="P17" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="Q17" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="R17">
         <v>1.2021509703101E+17</v>
       </c>
       <c r="S17" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="U17" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="V17" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="AA17" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="AC17" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -4648,46 +4609,46 @@
         <v>3</v>
       </c>
       <c r="BC17" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="BD17">
         <v>9</v>
       </c>
       <c r="BE17" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="BF17">
         <v>1512</v>
       </c>
       <c r="BG17" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="BH17">
         <v>7</v>
       </c>
       <c r="BI17" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="BJ17" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK17" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL17" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="BM17" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="BN17" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="BO17" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="BP17" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="BQ17">
         <v>11</v>
@@ -4696,25 +4657,25 @@
         <v>101</v>
       </c>
       <c r="BS17" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="BT17">
         <v>2251</v>
       </c>
       <c r="BU17" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="BV17" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="BW17">
         <v>60000</v>
       </c>
       <c r="BX17" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY17" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ17">
         <v>2026</v>
@@ -4723,19 +4684,19 @@
         <v>50</v>
       </c>
       <c r="CB17" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="CC17" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="CD17" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="CE17" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE17" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="18" spans="1:109">
@@ -4746,52 +4707,52 @@
         <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D18" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E18" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="F18">
         <v>543813007337</v>
       </c>
       <c r="G18" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H18" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I18">
         <v>231</v>
       </c>
       <c r="J18" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M18">
         <v>18</v>
       </c>
       <c r="S18" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="U18" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="V18" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="AA18" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="AC18" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -4800,46 +4761,46 @@
         <v>3</v>
       </c>
       <c r="BC18" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="BD18">
         <v>9</v>
       </c>
       <c r="BE18" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="BF18">
         <v>1512</v>
       </c>
       <c r="BG18" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="BH18">
         <v>7</v>
       </c>
       <c r="BI18" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="BJ18" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK18" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL18" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="BM18" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="BN18" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="BO18" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="BP18" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="BQ18">
         <v>11</v>
@@ -4848,25 +4809,25 @@
         <v>101</v>
       </c>
       <c r="BS18" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="BT18">
         <v>2251</v>
       </c>
       <c r="BU18" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="BV18" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="BW18">
         <v>60000</v>
       </c>
       <c r="BX18" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY18" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ18">
         <v>2026</v>
@@ -4875,19 +4836,19 @@
         <v>50</v>
       </c>
       <c r="CB18" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="CC18" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="CD18" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="CE18" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE18" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="19" spans="1:109">
@@ -4898,52 +4859,52 @@
         <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D19" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E19" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F19">
         <v>5493876116543</v>
       </c>
       <c r="G19" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H19" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I19">
         <v>11</v>
       </c>
       <c r="J19" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="K19">
         <v>3</v>
       </c>
       <c r="L19" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="M19">
         <v>41</v>
       </c>
       <c r="S19" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="U19" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="V19" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="AA19" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="AC19" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -4952,46 +4913,46 @@
         <v>1</v>
       </c>
       <c r="BC19" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD19">
         <v>24</v>
       </c>
       <c r="BE19" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF19">
         <v>1050</v>
       </c>
       <c r="BG19" t="s">
+        <v>320</v>
+      </c>
+      <c r="BH19">
+        <v>1</v>
+      </c>
+      <c r="BI19" t="s">
+        <v>331</v>
+      </c>
+      <c r="BJ19" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK19" t="s">
         <v>333</v>
       </c>
-      <c r="BH19">
-        <v>1</v>
-      </c>
-      <c r="BI19" t="s">
-        <v>344</v>
-      </c>
-      <c r="BJ19" t="s">
-        <v>345</v>
-      </c>
-      <c r="BK19" t="s">
-        <v>346</v>
-      </c>
       <c r="BL19" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="BM19" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="BN19" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="BO19" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="BP19" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="BQ19">
         <v>1</v>
@@ -5000,40 +4961,40 @@
         <v>3</v>
       </c>
       <c r="BS19" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT19">
         <v>10</v>
       </c>
       <c r="BU19" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="BV19" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="BW19">
         <v>56500</v>
       </c>
       <c r="BX19" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY19" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ19">
         <v>2026</v>
       </c>
       <c r="CC19" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="CD19" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="CE19" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE19" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" spans="1:109">
@@ -5044,49 +5005,49 @@
         <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D20" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E20" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F20">
         <v>5493876116543</v>
       </c>
       <c r="G20" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H20" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I20">
         <v>14</v>
       </c>
       <c r="J20" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="K20">
         <v>3</v>
       </c>
       <c r="L20" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="M20">
         <v>3</v>
       </c>
       <c r="U20" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="V20" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="AA20" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="AC20" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -5095,46 +5056,46 @@
         <v>1</v>
       </c>
       <c r="BC20" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD20">
         <v>24</v>
       </c>
       <c r="BE20" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF20">
         <v>1050</v>
       </c>
       <c r="BG20" t="s">
+        <v>320</v>
+      </c>
+      <c r="BH20">
+        <v>1</v>
+      </c>
+      <c r="BI20" t="s">
+        <v>331</v>
+      </c>
+      <c r="BJ20" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK20" t="s">
         <v>333</v>
       </c>
-      <c r="BH20">
-        <v>1</v>
-      </c>
-      <c r="BI20" t="s">
-        <v>344</v>
-      </c>
-      <c r="BJ20" t="s">
-        <v>345</v>
-      </c>
-      <c r="BK20" t="s">
-        <v>346</v>
-      </c>
       <c r="BL20" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="BM20" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="BN20" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="BO20" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="BP20" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="BQ20">
         <v>1</v>
@@ -5143,40 +5104,40 @@
         <v>3</v>
       </c>
       <c r="BS20" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT20">
         <v>10</v>
       </c>
       <c r="BU20" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="BV20" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="BW20">
         <v>56500</v>
       </c>
       <c r="BX20" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY20" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ20">
         <v>2026</v>
       </c>
       <c r="CC20" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="CD20" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="CE20" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE20" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="21" spans="1:109">
@@ -5184,43 +5145,43 @@
         <v>1525685</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D21" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E21" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="F21">
         <v>3874159718</v>
       </c>
       <c r="G21" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H21" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I21">
         <v>14</v>
       </c>
       <c r="J21" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="U21" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="V21" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="AC21" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="AD21">
         <v>1</v>
@@ -5229,46 +5190,46 @@
         <v>1</v>
       </c>
       <c r="BC21" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD21">
         <v>24</v>
       </c>
       <c r="BE21" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF21">
         <v>1157</v>
       </c>
       <c r="BG21" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="BH21">
         <v>1</v>
       </c>
       <c r="BI21" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ21" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK21" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL21" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="BM21" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="BN21" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="BO21" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="BP21" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="BQ21">
         <v>1</v>
@@ -5277,25 +5238,25 @@
         <v>3</v>
       </c>
       <c r="BS21" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT21">
         <v>1731</v>
       </c>
       <c r="BU21" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="BV21" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="BW21">
         <v>90300</v>
       </c>
       <c r="BX21" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY21" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ21">
         <v>2026</v>
@@ -5304,19 +5265,19 @@
         <v>50</v>
       </c>
       <c r="CB21" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="CC21" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="CD21" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="CE21" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE21" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="22" spans="1:109">
@@ -5324,52 +5285,52 @@
         <v>1560194</v>
       </c>
       <c r="C22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D22" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E22" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="F22">
         <v>543875900111</v>
       </c>
       <c r="G22" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H22" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I22">
         <v>94</v>
       </c>
       <c r="J22" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M22">
         <v>18</v>
       </c>
       <c r="S22" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="U22" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="V22" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="AA22" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="AC22" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -5378,46 +5339,46 @@
         <v>3</v>
       </c>
       <c r="BC22" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="BD22">
         <v>1</v>
       </c>
       <c r="BE22" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="BF22">
         <v>1681</v>
       </c>
       <c r="BG22" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="BH22">
         <v>7</v>
       </c>
       <c r="BI22" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="BJ22" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK22" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL22" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="BM22" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="BN22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="BO22" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="BP22" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="BQ22">
         <v>11</v>
@@ -5426,25 +5387,25 @@
         <v>2</v>
       </c>
       <c r="BS22" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="BT22">
         <v>1334</v>
       </c>
       <c r="BU22" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="BV22" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="BW22">
         <v>50000</v>
       </c>
       <c r="BX22" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY22" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ22">
         <v>2026</v>
@@ -5453,19 +5414,19 @@
         <v>50</v>
       </c>
       <c r="CB22" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="CC22" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="CD22" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="CE22" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="DE22" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="23" spans="1:109">
@@ -5476,70 +5437,70 @@
         <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F23">
         <v>5493875911005</v>
       </c>
       <c r="G23" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H23" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I23">
         <v>292</v>
       </c>
       <c r="J23" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M23">
         <v>908</v>
       </c>
       <c r="N23" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="O23" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="P23" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="Q23" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="R23">
         <v>1.2023729650832E+17</v>
       </c>
       <c r="T23" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="U23" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="V23" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="W23" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="Y23" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="AA23" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AC23" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -5548,46 +5509,46 @@
         <v>1</v>
       </c>
       <c r="BC23" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD23">
         <v>24</v>
       </c>
       <c r="BE23" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF23">
         <v>964</v>
       </c>
       <c r="BG23" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="BH23">
         <v>1</v>
       </c>
       <c r="BI23" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ23" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK23" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL23" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="BM23" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="BN23" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="BO23" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="BP23" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="BQ23">
         <v>1</v>
@@ -5596,40 +5557,40 @@
         <v>3</v>
       </c>
       <c r="BS23" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT23">
         <v>1731</v>
       </c>
       <c r="BU23" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="BV23" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="BW23">
         <v>56500</v>
       </c>
       <c r="BX23" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY23" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="BZ23">
         <v>2026</v>
       </c>
       <c r="CC23" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="CD23" t="s">
+        <v>487</v>
+      </c>
+      <c r="CE23" t="s">
         <v>500</v>
       </c>
-      <c r="CE23" t="s">
-        <v>513</v>
-      </c>
       <c r="DE23" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="24" spans="1:109">
@@ -5640,70 +5601,70 @@
         <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D24" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F24">
         <v>5493875911005</v>
       </c>
       <c r="G24" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H24" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I24">
         <v>360</v>
       </c>
       <c r="J24" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="K24">
         <v>3</v>
       </c>
       <c r="L24" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="M24">
         <v>443</v>
       </c>
       <c r="N24" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="O24" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="P24" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="Q24" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="R24">
         <v>1.2023893598175E+17</v>
       </c>
       <c r="T24" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="U24" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="V24" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="W24" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="Y24" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="AA24" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AC24" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -5712,46 +5673,46 @@
         <v>1</v>
       </c>
       <c r="BC24" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD24">
         <v>24</v>
       </c>
       <c r="BE24" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF24">
         <v>964</v>
       </c>
       <c r="BG24" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="BH24">
         <v>1</v>
       </c>
       <c r="BI24" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ24" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK24" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL24" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="BM24" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="BN24" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="BO24" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="BP24" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="BQ24">
         <v>1</v>
@@ -5760,40 +5721,40 @@
         <v>3</v>
       </c>
       <c r="BS24" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT24">
         <v>1731</v>
       </c>
       <c r="BU24" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="BV24" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="BW24">
         <v>56500</v>
       </c>
       <c r="BX24" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY24" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="BZ24">
         <v>2026</v>
       </c>
       <c r="CC24" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="CD24" t="s">
+        <v>487</v>
+      </c>
+      <c r="CE24" t="s">
         <v>500</v>
       </c>
-      <c r="CE24" t="s">
-        <v>513</v>
-      </c>
       <c r="DE24" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25" spans="1:109">
@@ -5804,46 +5765,46 @@
         <v>118</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D25" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F25">
         <v>5492235944297</v>
       </c>
       <c r="G25" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H25" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I25">
         <v>161</v>
       </c>
       <c r="J25" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="K25">
         <v>3</v>
       </c>
       <c r="L25" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="M25">
         <v>18</v>
       </c>
       <c r="S25" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="U25" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="V25" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="AC25" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -5852,46 +5813,46 @@
         <v>3</v>
       </c>
       <c r="BC25" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="BD25">
         <v>21</v>
       </c>
       <c r="BE25" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="BF25">
         <v>1225</v>
       </c>
       <c r="BG25" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="BH25">
         <v>7</v>
       </c>
       <c r="BI25" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="BJ25" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK25" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL25" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="BM25" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="BN25" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="BO25" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="BP25" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="BQ25">
         <v>11</v>
@@ -5900,25 +5861,25 @@
         <v>101</v>
       </c>
       <c r="BS25" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="BT25">
         <v>1010</v>
       </c>
       <c r="BU25" t="s">
+        <v>420</v>
+      </c>
+      <c r="BV25" t="s">
         <v>433</v>
-      </c>
-      <c r="BV25" t="s">
-        <v>446</v>
       </c>
       <c r="BW25">
         <v>45000</v>
       </c>
       <c r="BX25" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY25" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ25">
         <v>2026</v>
@@ -5927,19 +5888,19 @@
         <v>50</v>
       </c>
       <c r="CB25" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="CC25" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="CD25" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="CE25" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="DE25" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="26" spans="1:109">
@@ -5947,46 +5908,46 @@
         <v>1600059</v>
       </c>
       <c r="C26" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D26" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F26">
         <v>5493874524097</v>
       </c>
       <c r="G26" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H26" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I26">
         <v>383</v>
       </c>
       <c r="J26" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="K26">
         <v>3</v>
       </c>
       <c r="L26" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="M26">
         <v>18</v>
       </c>
       <c r="S26" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="U26" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="V26" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="AC26" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -5995,46 +5956,46 @@
         <v>3</v>
       </c>
       <c r="BC26" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="BD26">
         <v>1</v>
       </c>
       <c r="BE26" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="BF26">
         <v>1681</v>
       </c>
       <c r="BG26" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="BH26">
         <v>7</v>
       </c>
       <c r="BI26" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="BJ26" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK26" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL26" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="BM26" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="BN26" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="BO26" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="BP26" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="BQ26">
         <v>11</v>
@@ -6043,25 +6004,25 @@
         <v>3</v>
       </c>
       <c r="BS26" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT26">
         <v>1750</v>
       </c>
       <c r="BU26" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="BV26" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="BW26">
         <v>50000</v>
       </c>
       <c r="BX26" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY26" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ26">
         <v>2026</v>
@@ -6070,19 +6031,19 @@
         <v>50</v>
       </c>
       <c r="CB26" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="CC26" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="CD26" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="CE26" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="DE26" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="27" spans="1:109">
@@ -6090,46 +6051,46 @@
         <v>1523940</v>
       </c>
       <c r="C27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F27">
         <v>543874851679</v>
       </c>
       <c r="G27" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H27" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I27">
         <v>11</v>
       </c>
       <c r="J27" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M27">
         <v>4</v>
       </c>
       <c r="U27" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="V27" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="AA27" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="AC27" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -6138,46 +6099,46 @@
         <v>1</v>
       </c>
       <c r="BC27" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD27">
         <v>24</v>
       </c>
       <c r="BE27" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF27">
         <v>963</v>
       </c>
       <c r="BG27" t="s">
+        <v>324</v>
+      </c>
+      <c r="BH27">
+        <v>1</v>
+      </c>
+      <c r="BI27" t="s">
+        <v>331</v>
+      </c>
+      <c r="BJ27" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK27" t="s">
+        <v>333</v>
+      </c>
+      <c r="BL27" t="s">
         <v>337</v>
       </c>
-      <c r="BH27">
-        <v>1</v>
-      </c>
-      <c r="BI27" t="s">
-        <v>344</v>
-      </c>
-      <c r="BJ27" t="s">
-        <v>345</v>
-      </c>
-      <c r="BK27" t="s">
-        <v>346</v>
-      </c>
-      <c r="BL27" t="s">
-        <v>350</v>
-      </c>
       <c r="BM27" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="BN27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="BO27" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="BP27" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="BQ27">
         <v>1</v>
@@ -6186,25 +6147,25 @@
         <v>2</v>
       </c>
       <c r="BS27" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="BT27">
         <v>1334</v>
       </c>
       <c r="BU27" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="BV27" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="BW27">
         <v>113000</v>
       </c>
       <c r="BX27" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY27" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ27">
         <v>2026</v>
@@ -6213,19 +6174,19 @@
         <v>50</v>
       </c>
       <c r="CB27" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="CC27" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="CD27" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="CE27" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="DE27" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="28" spans="1:109">
@@ -6233,46 +6194,46 @@
         <v>1538226</v>
       </c>
       <c r="C28" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D28" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F28">
         <v>5493874851679</v>
       </c>
       <c r="G28" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H28" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I28">
         <v>11</v>
       </c>
       <c r="J28" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M28">
         <v>4</v>
       </c>
       <c r="U28" t="s">
+        <v>251</v>
+      </c>
+      <c r="V28" t="s">
         <v>260</v>
       </c>
-      <c r="V28" t="s">
-        <v>269</v>
-      </c>
       <c r="AA28" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="AC28" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="AD28">
         <v>1</v>
@@ -6281,46 +6242,46 @@
         <v>1</v>
       </c>
       <c r="BC28" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD28">
         <v>24</v>
       </c>
       <c r="BE28" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF28">
         <v>963</v>
       </c>
       <c r="BG28" t="s">
+        <v>324</v>
+      </c>
+      <c r="BH28">
+        <v>1</v>
+      </c>
+      <c r="BI28" t="s">
+        <v>331</v>
+      </c>
+      <c r="BJ28" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK28" t="s">
+        <v>333</v>
+      </c>
+      <c r="BL28" t="s">
         <v>337</v>
       </c>
-      <c r="BH28">
-        <v>1</v>
-      </c>
-      <c r="BI28" t="s">
-        <v>344</v>
-      </c>
-      <c r="BJ28" t="s">
-        <v>345</v>
-      </c>
-      <c r="BK28" t="s">
-        <v>346</v>
-      </c>
-      <c r="BL28" t="s">
-        <v>350</v>
-      </c>
       <c r="BM28" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="BN28" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="BO28" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="BP28" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="BQ28">
         <v>1</v>
@@ -6329,25 +6290,25 @@
         <v>2</v>
       </c>
       <c r="BS28" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="BT28">
         <v>1334</v>
       </c>
       <c r="BU28" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="BV28" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="BW28">
         <v>113000</v>
       </c>
       <c r="BX28" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY28" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="BZ28">
         <v>2026</v>
@@ -6356,147 +6317,162 @@
         <v>50</v>
       </c>
       <c r="CB28" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="CC28" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="CD28" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="CE28" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="DE28" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="29" spans="1:109">
       <c r="A29">
-        <v>1789735</v>
+        <v>1773800</v>
       </c>
       <c r="B29" t="s">
         <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>543875832169</v>
       </c>
       <c r="G29" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="H29" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="I29">
-        <v>360</v>
+        <v>31</v>
       </c>
       <c r="J29" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="K29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L29" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="M29">
-        <v>18</v>
+        <v>907</v>
       </c>
       <c r="S29" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="T29" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="U29" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="V29" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="W29" t="s">
-        <v>294</v>
+        <v>282</v>
+      </c>
+      <c r="X29" t="s">
+        <v>283</v>
       </c>
       <c r="Y29" t="s">
+        <v>286</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>166</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>246</v>
+      </c>
+      <c r="AC29" t="s">
         <v>298</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>172</v>
-      </c>
-      <c r="AB29" t="s">
-        <v>255</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>312</v>
       </c>
       <c r="AD29">
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC29" t="s">
-        <v>226</v>
+        <v>308</v>
       </c>
       <c r="BD29">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="BE29" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="BF29">
-        <v>1050</v>
+        <v>1588</v>
       </c>
       <c r="BG29" t="s">
+        <v>325</v>
+      </c>
+      <c r="BH29">
+        <v>7</v>
+      </c>
+      <c r="BI29" t="s">
+        <v>330</v>
+      </c>
+      <c r="BJ29" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK29" t="s">
         <v>333</v>
       </c>
-      <c r="BH29">
-        <v>1</v>
-      </c>
-      <c r="BI29" t="s">
-        <v>344</v>
-      </c>
-      <c r="BJ29" t="s">
-        <v>345</v>
-      </c>
-      <c r="BK29" t="s">
-        <v>346</v>
-      </c>
       <c r="BL29" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="BM29" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="BN29" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="BO29" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="BP29" t="s">
-        <v>418</v>
+        <v>390</v>
       </c>
       <c r="BQ29">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="BR29">
+        <v>3</v>
+      </c>
+      <c r="BS29" t="s">
+        <v>411</v>
+      </c>
+      <c r="BT29">
+        <v>2191</v>
+      </c>
+      <c r="BU29" t="s">
+        <v>422</v>
       </c>
       <c r="BV29" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="BW29">
-        <v>56500</v>
+        <v>130000</v>
       </c>
       <c r="BX29" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="BY29" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="BZ29">
         <v>2026</v>
@@ -6505,150 +6481,150 @@
         <v>50</v>
       </c>
       <c r="CB29" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="CC29" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="CD29" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="CE29" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="DE29" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
     </row>
     <row r="30" spans="1:109">
       <c r="A30">
-        <v>1682222</v>
+        <v>1722167</v>
       </c>
       <c r="B30" t="s">
         <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
-        <v>173</v>
+        <v>167</v>
+      </c>
+      <c r="E30" t="s">
+        <v>184</v>
       </c>
       <c r="F30">
-        <v>5490000</v>
+        <v>5493885080215</v>
       </c>
       <c r="G30" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H30" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I30">
-        <v>393</v>
+        <v>113</v>
       </c>
       <c r="J30" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="K30">
+        <v>500</v>
+      </c>
+      <c r="L30" t="s">
+        <v>221</v>
+      </c>
+      <c r="M30">
         <v>3</v>
       </c>
-      <c r="L30" t="s">
-        <v>229</v>
-      </c>
-      <c r="M30">
-        <v>18</v>
-      </c>
       <c r="S30" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="T30" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="U30" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="V30" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="W30" t="s">
-        <v>294</v>
-      </c>
-      <c r="X30" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="Y30" t="s">
+        <v>286</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>246</v>
+      </c>
+      <c r="AC30" t="s">
         <v>298</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>173</v>
-      </c>
-      <c r="AB30" t="s">
-        <v>255</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>312</v>
       </c>
       <c r="AD30">
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="BC30" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="BD30">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BE30" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="BF30">
-        <v>1050</v>
+        <v>1583</v>
       </c>
       <c r="BG30" t="s">
+        <v>326</v>
+      </c>
+      <c r="BH30">
+        <v>7</v>
+      </c>
+      <c r="BI30" t="s">
+        <v>330</v>
+      </c>
+      <c r="BJ30" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK30" t="s">
         <v>333</v>
       </c>
-      <c r="BH30">
-        <v>1</v>
-      </c>
-      <c r="BI30" t="s">
-        <v>344</v>
-      </c>
-      <c r="BJ30" t="s">
-        <v>345</v>
-      </c>
-      <c r="BK30" t="s">
-        <v>346</v>
-      </c>
       <c r="BL30" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="BM30" t="s">
+        <v>361</v>
+      </c>
+      <c r="BN30" t="s">
         <v>373</v>
       </c>
-      <c r="BN30" t="s">
-        <v>385</v>
-      </c>
       <c r="BO30" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="BP30" t="s">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="BQ30">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BV30" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="BW30">
-        <v>56500</v>
+        <v>75000</v>
       </c>
       <c r="BX30" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="BY30" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="BZ30">
         <v>2026</v>
@@ -6657,138 +6633,150 @@
         <v>50</v>
       </c>
       <c r="CB30" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="CC30" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="CD30" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="CE30" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="DE30" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
     </row>
     <row r="31" spans="1:109">
       <c r="A31">
-        <v>1607267</v>
+        <v>1722165</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s">
-        <v>174</v>
+        <v>167</v>
+      </c>
+      <c r="E31" t="s">
+        <v>184</v>
       </c>
       <c r="F31">
-        <v>5490000</v>
+        <v>5493885080215</v>
       </c>
       <c r="G31" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="H31" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="I31">
-        <v>1201</v>
+        <v>113</v>
       </c>
       <c r="J31" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="L31" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="M31">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="S31" t="s">
-        <v>255</v>
+        <v>246</v>
+      </c>
+      <c r="T31" t="s">
+        <v>247</v>
       </c>
       <c r="U31" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="V31" t="s">
-        <v>281</v>
+        <v>271</v>
+      </c>
+      <c r="W31" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>286</v>
       </c>
       <c r="AA31" t="s">
-        <v>306</v>
+        <v>167</v>
       </c>
       <c r="AB31" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="AC31" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="AD31">
         <v>0</v>
       </c>
       <c r="BB31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="BC31" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="BD31">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BE31" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="BF31">
-        <v>1050</v>
+        <v>1583</v>
       </c>
       <c r="BG31" t="s">
+        <v>326</v>
+      </c>
+      <c r="BH31">
+        <v>7</v>
+      </c>
+      <c r="BI31" t="s">
+        <v>330</v>
+      </c>
+      <c r="BJ31" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK31" t="s">
         <v>333</v>
       </c>
-      <c r="BH31">
-        <v>1</v>
-      </c>
-      <c r="BI31" t="s">
-        <v>344</v>
-      </c>
-      <c r="BJ31" t="s">
-        <v>345</v>
-      </c>
-      <c r="BK31" t="s">
-        <v>346</v>
-      </c>
       <c r="BL31" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="BM31" t="s">
+        <v>361</v>
+      </c>
+      <c r="BN31" t="s">
         <v>373</v>
       </c>
-      <c r="BN31" t="s">
-        <v>385</v>
-      </c>
       <c r="BO31" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="BP31" t="s">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="BQ31">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BV31" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="BW31">
-        <v>56500</v>
+        <v>75000</v>
       </c>
       <c r="BX31" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="BY31" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="BZ31">
         <v>2026</v>
@@ -6797,75 +6785,78 @@
         <v>50</v>
       </c>
       <c r="CB31" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="CC31" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="CD31" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="CE31" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="DE31" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
     </row>
     <row r="32" spans="1:109">
       <c r="A32">
-        <v>1617917</v>
+        <v>1655372</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C32" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D32" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F32">
-        <v>5490000</v>
+        <v>543875016886</v>
       </c>
       <c r="G32" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H32" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="I32">
-        <v>393</v>
+        <v>187</v>
       </c>
       <c r="J32" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="K32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="M32">
-        <v>18</v>
-      </c>
-      <c r="S32" t="s">
-        <v>255</v>
+        <v>4</v>
+      </c>
+      <c r="N32" t="s">
+        <v>226</v>
+      </c>
+      <c r="O32" t="s">
+        <v>233</v>
+      </c>
+      <c r="P32" t="s">
+        <v>236</v>
       </c>
       <c r="U32" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="V32" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="AA32" t="s">
-        <v>307</v>
-      </c>
-      <c r="AB32" t="s">
-        <v>255</v>
+        <v>294</v>
       </c>
       <c r="AC32" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="AD32">
         <v>0</v>
@@ -6874,61 +6865,73 @@
         <v>1</v>
       </c>
       <c r="BC32" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD32">
         <v>24</v>
       </c>
       <c r="BE32" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF32">
-        <v>1050</v>
+        <v>965</v>
       </c>
       <c r="BG32" t="s">
+        <v>317</v>
+      </c>
+      <c r="BH32">
+        <v>1</v>
+      </c>
+      <c r="BI32" t="s">
+        <v>331</v>
+      </c>
+      <c r="BJ32" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK32" t="s">
         <v>333</v>
       </c>
-      <c r="BH32">
-        <v>1</v>
-      </c>
-      <c r="BI32" t="s">
-        <v>344</v>
-      </c>
-      <c r="BJ32" t="s">
-        <v>345</v>
-      </c>
-      <c r="BK32" t="s">
-        <v>346</v>
-      </c>
       <c r="BL32" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="BM32" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="BN32" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="BO32" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="BP32" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="BQ32">
         <v>1</v>
       </c>
+      <c r="BR32">
+        <v>3</v>
+      </c>
+      <c r="BS32" t="s">
+        <v>411</v>
+      </c>
+      <c r="BT32">
+        <v>1872</v>
+      </c>
+      <c r="BU32" t="s">
+        <v>423</v>
+      </c>
       <c r="BV32" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="BW32">
         <v>56500</v>
       </c>
       <c r="BX32" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="BY32" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="BZ32">
         <v>2026</v>
@@ -6937,162 +6940,144 @@
         <v>50</v>
       </c>
       <c r="CB32" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="CC32" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="CD32" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="CE32" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="DE32" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="33" spans="1:109">
       <c r="A33">
-        <v>1773800</v>
+        <v>1655511</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D33" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F33">
-        <v>543875832169</v>
+        <v>5493875016886</v>
       </c>
       <c r="G33" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H33" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I33">
-        <v>31</v>
+        <v>323</v>
       </c>
       <c r="J33" t="s">
+        <v>209</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33" t="s">
         <v>217</v>
       </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-      <c r="L33" t="s">
-        <v>226</v>
-      </c>
       <c r="M33">
-        <v>907</v>
-      </c>
-      <c r="S33" t="s">
-        <v>255</v>
-      </c>
-      <c r="T33" t="s">
-        <v>256</v>
+        <v>18</v>
       </c>
       <c r="U33" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="V33" t="s">
-        <v>283</v>
-      </c>
-      <c r="W33" t="s">
+        <v>272</v>
+      </c>
+      <c r="AA33" t="s">
         <v>294</v>
       </c>
-      <c r="X33" t="s">
-        <v>296</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>298</v>
-      </c>
-      <c r="AA33" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB33" t="s">
-        <v>255</v>
-      </c>
       <c r="AC33" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="AD33">
         <v>0</v>
       </c>
       <c r="BB33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC33" t="s">
-        <v>321</v>
+        <v>217</v>
       </c>
       <c r="BD33">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="BE33" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="BF33">
-        <v>1588</v>
+        <v>965</v>
       </c>
       <c r="BG33" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="BH33">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BI33" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="BJ33" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK33" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL33" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="BM33" t="s">
+        <v>362</v>
+      </c>
+      <c r="BN33" t="s">
         <v>374</v>
       </c>
-      <c r="BN33" t="s">
-        <v>386</v>
-      </c>
       <c r="BO33" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="BP33" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="BQ33">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="BR33">
         <v>3</v>
       </c>
       <c r="BS33" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT33">
-        <v>2191</v>
+        <v>1872</v>
       </c>
       <c r="BU33" t="s">
+        <v>423</v>
+      </c>
+      <c r="BV33" t="s">
         <v>435</v>
       </c>
-      <c r="BV33" t="s">
-        <v>448</v>
-      </c>
       <c r="BW33">
-        <v>130000</v>
+        <v>56500</v>
       </c>
       <c r="BX33" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY33" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="BZ33">
         <v>2026</v>
@@ -7101,150 +7086,144 @@
         <v>50</v>
       </c>
       <c r="CB33" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="CC33" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="CD33" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="CE33" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="DE33" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
     </row>
     <row r="34" spans="1:109">
       <c r="A34">
-        <v>1722167</v>
+        <v>1655980</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C34" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D34" t="s">
-        <v>177</v>
-      </c>
-      <c r="E34" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="F34">
-        <v>5493885080215</v>
+        <v>5493875016886</v>
       </c>
       <c r="G34" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H34" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I34">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="J34" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="K34">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="L34" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="M34">
-        <v>3</v>
-      </c>
-      <c r="S34" t="s">
-        <v>255</v>
-      </c>
-      <c r="T34" t="s">
-        <v>256</v>
+        <v>18</v>
       </c>
       <c r="U34" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="V34" t="s">
-        <v>284</v>
-      </c>
-      <c r="W34" t="s">
+        <v>273</v>
+      </c>
+      <c r="AA34" t="s">
         <v>294</v>
       </c>
-      <c r="Y34" t="s">
-        <v>298</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>177</v>
-      </c>
-      <c r="AB34" t="s">
-        <v>255</v>
-      </c>
       <c r="AC34" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="AD34">
         <v>0</v>
       </c>
       <c r="BB34">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BC34" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="BD34">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BE34" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="BF34">
-        <v>1583</v>
+        <v>965</v>
       </c>
       <c r="BG34" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="BH34">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BI34" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="BJ34" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK34" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL34" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="BM34" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="BN34" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="BO34" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="BP34" t="s">
         <v>405</v>
       </c>
       <c r="BQ34">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="BR34">
+        <v>3</v>
+      </c>
+      <c r="BS34" t="s">
+        <v>411</v>
+      </c>
+      <c r="BT34">
+        <v>1872</v>
+      </c>
+      <c r="BU34" t="s">
+        <v>423</v>
       </c>
       <c r="BV34" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="BW34">
-        <v>75000</v>
+        <v>56500</v>
       </c>
       <c r="BX34" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="BY34" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="BZ34">
         <v>2026</v>
@@ -7253,150 +7232,144 @@
         <v>50</v>
       </c>
       <c r="CB34" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="CC34" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="CD34" t="s">
+        <v>493</v>
+      </c>
+      <c r="CE34" t="s">
+        <v>502</v>
+      </c>
+      <c r="DE34" t="s">
         <v>506</v>
-      </c>
-      <c r="CE34" t="s">
-        <v>514</v>
-      </c>
-      <c r="DE34" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="35" spans="1:109">
       <c r="A35">
-        <v>1722165</v>
+        <v>1656943</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C35" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D35" t="s">
-        <v>177</v>
-      </c>
-      <c r="E35" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="F35">
-        <v>5493885080215</v>
+        <v>5493875016886</v>
       </c>
       <c r="G35" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H35" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I35">
-        <v>113</v>
+        <v>395</v>
       </c>
       <c r="J35" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="K35">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="L35" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="M35">
-        <v>3</v>
-      </c>
-      <c r="S35" t="s">
-        <v>255</v>
-      </c>
-      <c r="T35" t="s">
-        <v>256</v>
+        <v>18</v>
       </c>
       <c r="U35" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="V35" t="s">
-        <v>284</v>
-      </c>
-      <c r="W35" t="s">
+        <v>274</v>
+      </c>
+      <c r="AA35" t="s">
         <v>294</v>
       </c>
-      <c r="Y35" t="s">
-        <v>298</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>177</v>
-      </c>
-      <c r="AB35" t="s">
-        <v>255</v>
-      </c>
       <c r="AC35" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="AD35">
         <v>0</v>
       </c>
       <c r="BB35">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BC35" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="BD35">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BE35" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="BF35">
-        <v>1583</v>
+        <v>965</v>
       </c>
       <c r="BG35" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="BH35">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BI35" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="BJ35" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK35" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL35" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="BM35" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="BN35" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="BO35" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="BP35" t="s">
         <v>405</v>
       </c>
       <c r="BQ35">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="BR35">
+        <v>3</v>
+      </c>
+      <c r="BS35" t="s">
+        <v>411</v>
+      </c>
+      <c r="BT35">
+        <v>1872</v>
+      </c>
+      <c r="BU35" t="s">
+        <v>423</v>
       </c>
       <c r="BV35" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="BW35">
-        <v>75000</v>
+        <v>56500</v>
       </c>
       <c r="BX35" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="BY35" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="BZ35">
         <v>2026</v>
@@ -7405,78 +7378,69 @@
         <v>50</v>
       </c>
       <c r="CB35" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="CC35" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="CD35" t="s">
+        <v>493</v>
+      </c>
+      <c r="CE35" t="s">
+        <v>502</v>
+      </c>
+      <c r="DE35" t="s">
         <v>506</v>
-      </c>
-      <c r="CE35" t="s">
-        <v>514</v>
-      </c>
-      <c r="DE35" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="36" spans="1:109">
       <c r="A36">
-        <v>1655372</v>
-      </c>
-      <c r="B36" t="s">
-        <v>125</v>
+        <v>1529143</v>
       </c>
       <c r="C36" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D36" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="F36">
         <v>543875016886</v>
       </c>
       <c r="G36" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H36" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I36">
-        <v>187</v>
+        <v>1201</v>
       </c>
       <c r="J36" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M36">
-        <v>4</v>
-      </c>
-      <c r="N36" t="s">
-        <v>235</v>
-      </c>
-      <c r="O36" t="s">
-        <v>242</v>
-      </c>
-      <c r="P36" t="s">
-        <v>245</v>
+        <v>18</v>
       </c>
       <c r="U36" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="V36" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="AA36" t="s">
-        <v>308</v>
+        <v>294</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>246</v>
       </c>
       <c r="AC36" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="AD36">
         <v>0</v>
@@ -7485,46 +7449,46 @@
         <v>1</v>
       </c>
       <c r="BC36" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD36">
         <v>24</v>
       </c>
       <c r="BE36" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF36">
         <v>965</v>
       </c>
       <c r="BG36" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="BH36">
         <v>1</v>
       </c>
       <c r="BI36" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ36" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK36" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL36" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="BM36" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="BN36" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="BO36" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="BP36" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="BQ36">
         <v>1</v>
@@ -7533,25 +7497,25 @@
         <v>3</v>
       </c>
       <c r="BS36" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT36">
         <v>1872</v>
       </c>
       <c r="BU36" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="BV36" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="BW36">
         <v>56500</v>
       </c>
       <c r="BX36" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY36" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="BZ36">
         <v>2026</v>
@@ -7560,69 +7524,72 @@
         <v>50</v>
       </c>
       <c r="CB36" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="CC36" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="CD36" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="CE36" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="DE36" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="37" spans="1:109">
       <c r="A37">
-        <v>1655511</v>
+        <v>1632747</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D37" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F37">
-        <v>5493875016886</v>
+        <v>543872132387</v>
       </c>
       <c r="G37" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H37" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I37">
-        <v>323</v>
+        <v>26</v>
       </c>
       <c r="J37" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="K37">
         <v>1</v>
       </c>
       <c r="L37" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M37">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="U37" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="V37" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="AA37" t="s">
-        <v>308</v>
+        <v>295</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>246</v>
       </c>
       <c r="AC37" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="AD37">
         <v>0</v>
@@ -7631,46 +7598,46 @@
         <v>1</v>
       </c>
       <c r="BC37" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD37">
         <v>24</v>
       </c>
       <c r="BE37" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF37">
-        <v>965</v>
+        <v>1050</v>
       </c>
       <c r="BG37" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="BH37">
         <v>1</v>
       </c>
       <c r="BI37" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ37" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK37" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL37" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="BM37" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="BN37" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="BO37" t="s">
+        <v>393</v>
+      </c>
+      <c r="BP37" t="s">
         <v>406</v>
-      </c>
-      <c r="BP37" t="s">
-        <v>419</v>
       </c>
       <c r="BQ37">
         <v>1</v>
@@ -7679,171 +7646,183 @@
         <v>3</v>
       </c>
       <c r="BS37" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="BT37">
-        <v>1872</v>
+        <v>1750</v>
       </c>
       <c r="BU37" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="BV37" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="BW37">
         <v>56500</v>
       </c>
       <c r="BX37" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY37" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="BZ37">
         <v>2026</v>
       </c>
-      <c r="CA37">
-        <v>50</v>
-      </c>
-      <c r="CB37" t="s">
-        <v>470</v>
-      </c>
       <c r="CC37" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="CD37" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="CE37" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="DE37" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="38" spans="1:109">
       <c r="A38">
-        <v>1655980</v>
+        <v>1775443</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C38" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F38">
-        <v>5493875016886</v>
+        <v>3815765777</v>
       </c>
       <c r="G38" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H38" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I38">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J38" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="K38">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="L38" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="M38">
         <v>18</v>
       </c>
+      <c r="S38" t="s">
+        <v>246</v>
+      </c>
+      <c r="T38" t="s">
+        <v>248</v>
+      </c>
       <c r="U38" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="V38" t="s">
+        <v>277</v>
+      </c>
+      <c r="W38" t="s">
+        <v>282</v>
+      </c>
+      <c r="X38" t="s">
+        <v>284</v>
+      </c>
+      <c r="Y38" t="s">
         <v>286</v>
       </c>
       <c r="AA38" t="s">
-        <v>308</v>
+        <v>170</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>297</v>
       </c>
       <c r="AC38" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="AD38">
         <v>0</v>
       </c>
       <c r="BB38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC38" t="s">
-        <v>226</v>
+        <v>308</v>
       </c>
       <c r="BD38">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BE38" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="BF38">
-        <v>965</v>
+        <v>1651</v>
       </c>
       <c r="BG38" t="s">
+        <v>327</v>
+      </c>
+      <c r="BH38">
+        <v>7</v>
+      </c>
+      <c r="BI38" t="s">
         <v>330</v>
       </c>
-      <c r="BH38">
-        <v>1</v>
-      </c>
-      <c r="BI38" t="s">
-        <v>344</v>
-      </c>
       <c r="BJ38" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK38" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL38" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="BM38" t="s">
+        <v>364</v>
+      </c>
+      <c r="BN38" t="s">
         <v>376</v>
       </c>
-      <c r="BN38" t="s">
-        <v>388</v>
-      </c>
       <c r="BO38" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="BP38" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="BQ38">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BR38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS38" t="s">
+        <v>410</v>
+      </c>
+      <c r="BT38">
+        <v>2371</v>
+      </c>
+      <c r="BU38" t="s">
         <v>424</v>
       </c>
-      <c r="BT38">
-        <v>1872</v>
-      </c>
-      <c r="BU38" t="s">
-        <v>436</v>
-      </c>
       <c r="BV38" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="BW38">
-        <v>56500</v>
+        <v>36000</v>
       </c>
       <c r="BX38" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="BY38" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="BZ38">
         <v>2026</v>
@@ -7852,69 +7831,84 @@
         <v>50</v>
       </c>
       <c r="CB38" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="CC38" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="CD38" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="CE38" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="DE38" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
     </row>
     <row r="39" spans="1:109">
       <c r="A39">
-        <v>1656943</v>
+        <v>1692954</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D39" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F39">
-        <v>5493875016886</v>
+        <v>5493835518006</v>
       </c>
       <c r="G39" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H39" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="I39">
-        <v>395</v>
+        <v>336</v>
       </c>
       <c r="J39" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="K39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="M39">
         <v>18</v>
       </c>
+      <c r="T39" t="s">
+        <v>248</v>
+      </c>
       <c r="U39" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="V39" t="s">
-        <v>287</v>
+        <v>278</v>
+      </c>
+      <c r="W39" t="s">
+        <v>282</v>
+      </c>
+      <c r="X39" t="s">
+        <v>285</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>286</v>
       </c>
       <c r="AA39" t="s">
-        <v>308</v>
+        <v>171</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>246</v>
       </c>
       <c r="AC39" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -7923,73 +7917,61 @@
         <v>1</v>
       </c>
       <c r="BC39" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD39">
         <v>24</v>
       </c>
       <c r="BE39" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF39">
-        <v>965</v>
+        <v>1050</v>
       </c>
       <c r="BG39" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="BH39">
         <v>1</v>
       </c>
       <c r="BI39" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="BJ39" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK39" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="BL39" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="BM39" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="BN39" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="BO39" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="BP39" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="BQ39">
         <v>1</v>
       </c>
-      <c r="BR39">
-        <v>3</v>
-      </c>
-      <c r="BS39" t="s">
-        <v>424</v>
-      </c>
-      <c r="BT39">
-        <v>1872</v>
-      </c>
-      <c r="BU39" t="s">
-        <v>436</v>
-      </c>
       <c r="BV39" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="BW39">
         <v>56500</v>
       </c>
       <c r="BX39" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="BY39" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="BZ39">
         <v>2026</v>
@@ -7998,144 +7980,138 @@
         <v>50</v>
       </c>
       <c r="CB39" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="CC39" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="CD39" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="CE39" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="DE39" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
     </row>
     <row r="40" spans="1:109">
       <c r="A40">
-        <v>1529143</v>
+        <v>1365200</v>
+      </c>
+      <c r="B40" t="s">
+        <v>125</v>
       </c>
       <c r="C40" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D40" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F40">
-        <v>543875016886</v>
+        <v>543464559391</v>
       </c>
       <c r="G40" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="H40" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="I40">
-        <v>1201</v>
+        <v>378</v>
       </c>
       <c r="J40" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K40">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="L40" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="M40">
         <v>18</v>
       </c>
+      <c r="S40" t="s">
+        <v>246</v>
+      </c>
+      <c r="T40" t="s">
+        <v>248</v>
+      </c>
       <c r="U40" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="V40" t="s">
-        <v>288</v>
+        <v>279</v>
+      </c>
+      <c r="W40" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>286</v>
       </c>
       <c r="AA40" t="s">
-        <v>308</v>
-      </c>
-      <c r="AB40" t="s">
-        <v>255</v>
-      </c>
-      <c r="AC40" t="s">
-        <v>317</v>
-      </c>
-      <c r="AD40">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="BB40">
         <v>1</v>
       </c>
       <c r="BC40" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD40">
         <v>24</v>
       </c>
       <c r="BE40" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF40">
-        <v>965</v>
+        <v>983</v>
       </c>
       <c r="BG40" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="BH40">
         <v>1</v>
       </c>
       <c r="BI40" t="s">
+        <v>331</v>
+      </c>
+      <c r="BJ40" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK40" t="s">
+        <v>333</v>
+      </c>
+      <c r="BL40" t="s">
         <v>344</v>
       </c>
-      <c r="BJ40" t="s">
-        <v>345</v>
-      </c>
-      <c r="BK40" t="s">
-        <v>346</v>
-      </c>
-      <c r="BL40" t="s">
-        <v>354</v>
-      </c>
       <c r="BM40" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="BN40" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="BO40" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="BP40" t="s">
-        <v>419</v>
+        <v>381</v>
       </c>
       <c r="BQ40">
         <v>1</v>
       </c>
-      <c r="BR40">
-        <v>3</v>
-      </c>
-      <c r="BS40" t="s">
-        <v>424</v>
-      </c>
-      <c r="BT40">
-        <v>1872</v>
-      </c>
-      <c r="BU40" t="s">
-        <v>436</v>
-      </c>
       <c r="BV40" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="BW40">
         <v>56500</v>
       </c>
       <c r="BX40" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="BY40" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="BZ40">
         <v>2026</v>
@@ -8144,230 +8120,236 @@
         <v>50</v>
       </c>
       <c r="CB40" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="CC40" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="CD40" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="CE40" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="DE40" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="41" spans="1:109">
       <c r="A41">
-        <v>1632747</v>
+        <v>1385414</v>
       </c>
       <c r="B41" t="s">
         <v>126</v>
       </c>
       <c r="C41" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D41" t="s">
-        <v>179</v>
+        <v>173</v>
+      </c>
+      <c r="E41" t="s">
+        <v>185</v>
       </c>
       <c r="F41">
-        <v>543872132387</v>
+        <v>543442305585</v>
       </c>
       <c r="G41" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="H41" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="I41">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J41" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="K41">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="L41" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M41">
-        <v>272</v>
+        <v>103</v>
+      </c>
+      <c r="N41" t="s">
+        <v>229</v>
+      </c>
+      <c r="O41" t="s">
+        <v>234</v>
+      </c>
+      <c r="P41" t="s">
+        <v>240</v>
+      </c>
+      <c r="T41" t="s">
+        <v>248</v>
       </c>
       <c r="U41" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="V41" t="s">
-        <v>289</v>
+        <v>280</v>
+      </c>
+      <c r="W41" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>286</v>
       </c>
       <c r="AA41" t="s">
-        <v>309</v>
-      </c>
-      <c r="AB41" t="s">
-        <v>255</v>
-      </c>
-      <c r="AC41" t="s">
-        <v>318</v>
-      </c>
-      <c r="AD41">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="BB41">
         <v>1</v>
       </c>
       <c r="BC41" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BD41">
         <v>24</v>
       </c>
       <c r="BE41" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="BF41">
         <v>1050</v>
       </c>
       <c r="BG41" t="s">
+        <v>320</v>
+      </c>
+      <c r="BH41">
+        <v>1</v>
+      </c>
+      <c r="BI41" t="s">
+        <v>331</v>
+      </c>
+      <c r="BJ41" t="s">
+        <v>332</v>
+      </c>
+      <c r="BK41" t="s">
         <v>333</v>
       </c>
-      <c r="BH41">
-        <v>1</v>
-      </c>
-      <c r="BI41" t="s">
-        <v>344</v>
-      </c>
-      <c r="BJ41" t="s">
+      <c r="BL41" t="s">
         <v>345</v>
       </c>
-      <c r="BK41" t="s">
-        <v>346</v>
-      </c>
-      <c r="BL41" t="s">
-        <v>355</v>
-      </c>
       <c r="BM41" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="BN41" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="BO41" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="BP41" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="BQ41">
         <v>1</v>
       </c>
-      <c r="BR41">
-        <v>3</v>
-      </c>
-      <c r="BS41" t="s">
-        <v>424</v>
-      </c>
-      <c r="BT41">
-        <v>1750</v>
-      </c>
-      <c r="BU41" t="s">
-        <v>434</v>
-      </c>
       <c r="BV41" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="BW41">
         <v>56500</v>
       </c>
       <c r="BX41" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="BY41" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="BZ41">
         <v>2026</v>
       </c>
+      <c r="CA41">
+        <v>50</v>
+      </c>
+      <c r="CB41" t="s">
+        <v>460</v>
+      </c>
       <c r="CC41" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="CD41" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="CE41" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="DE41" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="42" spans="1:109">
       <c r="A42">
-        <v>1775443</v>
+        <v>1663213</v>
       </c>
       <c r="B42" t="s">
         <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D42" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F42">
-        <v>3815765777</v>
+        <v>5493873256079</v>
       </c>
       <c r="G42" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H42" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I42">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="J42" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="K42">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="L42" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="M42">
-        <v>18</v>
-      </c>
-      <c r="S42" t="s">
-        <v>255</v>
-      </c>
-      <c r="T42" t="s">
-        <v>257</v>
+        <v>297</v>
+      </c>
+      <c r="N42" t="s">
+        <v>226</v>
+      </c>
+      <c r="O42" t="s">
+        <v>235</v>
+      </c>
+      <c r="P42" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>245</v>
+      </c>
+      <c r="R42">
+        <v>551860803098</v>
       </c>
       <c r="U42" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="V42" t="s">
-        <v>290</v>
-      </c>
-      <c r="W42" t="s">
-        <v>294</v>
-      </c>
-      <c r="X42" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y42" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="AA42" t="s">
-        <v>180</v>
+        <v>296</v>
       </c>
       <c r="AB42" t="s">
-        <v>311</v>
+        <v>246</v>
       </c>
       <c r="AC42" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="AD42">
         <v>0</v>
@@ -8376,73 +8358,73 @@
         <v>3</v>
       </c>
       <c r="BC42" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="BD42">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BE42" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="BF42">
-        <v>1651</v>
+        <v>1716</v>
       </c>
       <c r="BG42" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="BH42">
         <v>7</v>
       </c>
       <c r="BI42" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="BJ42" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="BK42" t="s">
+        <v>333</v>
+      </c>
+      <c r="BL42" t="s">
         <v>346</v>
       </c>
-      <c r="BL42" t="s">
-        <v>356</v>
-      </c>
       <c r="BM42" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="BN42" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="BO42" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="BP42" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="BQ42">
         <v>11</v>
       </c>
       <c r="BR42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS42" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="BT42">
-        <v>2371</v>
+        <v>2411</v>
       </c>
       <c r="BU42" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="BV42" t="s">
+        <v>426</v>
+      </c>
+      <c r="BW42">
+        <v>75000</v>
+      </c>
+      <c r="BX42" t="s">
         <v>439</v>
       </c>
-      <c r="BW42">
-        <v>36000</v>
-      </c>
-      <c r="BX42" t="s">
-        <v>452</v>
-      </c>
       <c r="BY42" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="BZ42">
         <v>2026</v>
@@ -8451,472 +8433,19 @@
         <v>50</v>
       </c>
       <c r="CB42" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="CC42" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="CD42" t="s">
-        <v>509</v>
+        <v>174</v>
       </c>
       <c r="CE42" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="DE42" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="43" spans="1:109">
-      <c r="A43">
-        <v>1365200</v>
-      </c>
-      <c r="B43" t="s">
-        <v>128</v>
-      </c>
-      <c r="C43" t="s">
-        <v>153</v>
-      </c>
-      <c r="D43" t="s">
-        <v>181</v>
-      </c>
-      <c r="F43">
-        <v>543464559391</v>
-      </c>
-      <c r="G43" t="s">
-        <v>196</v>
-      </c>
-      <c r="H43" t="s">
-        <v>198</v>
-      </c>
-      <c r="I43">
-        <v>378</v>
-      </c>
-      <c r="J43" t="s">
-        <v>224</v>
-      </c>
-      <c r="K43">
-        <v>62</v>
-      </c>
-      <c r="L43" t="s">
-        <v>232</v>
-      </c>
-      <c r="M43">
-        <v>18</v>
-      </c>
-      <c r="S43" t="s">
-        <v>255</v>
-      </c>
-      <c r="T43" t="s">
-        <v>257</v>
-      </c>
-      <c r="U43" t="s">
-        <v>259</v>
-      </c>
-      <c r="V43" t="s">
-        <v>291</v>
-      </c>
-      <c r="W43" t="s">
-        <v>294</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>298</v>
-      </c>
-      <c r="AA43" t="s">
-        <v>181</v>
-      </c>
-      <c r="BB43">
-        <v>1</v>
-      </c>
-      <c r="BC43" t="s">
-        <v>226</v>
-      </c>
-      <c r="BD43">
-        <v>24</v>
-      </c>
-      <c r="BE43" t="s">
-        <v>323</v>
-      </c>
-      <c r="BF43">
-        <v>983</v>
-      </c>
-      <c r="BG43" t="s">
-        <v>341</v>
-      </c>
-      <c r="BH43">
-        <v>1</v>
-      </c>
-      <c r="BI43" t="s">
-        <v>344</v>
-      </c>
-      <c r="BJ43" t="s">
-        <v>345</v>
-      </c>
-      <c r="BK43" t="s">
-        <v>346</v>
-      </c>
-      <c r="BL43" t="s">
-        <v>357</v>
-      </c>
-      <c r="BM43" t="s">
-        <v>379</v>
-      </c>
-      <c r="BN43" t="s">
-        <v>391</v>
-      </c>
-      <c r="BO43" t="s">
-        <v>394</v>
-      </c>
-      <c r="BP43" t="s">
-        <v>394</v>
-      </c>
-      <c r="BQ43">
-        <v>1</v>
-      </c>
-      <c r="BV43" t="s">
-        <v>439</v>
-      </c>
-      <c r="BW43">
-        <v>56500</v>
-      </c>
-      <c r="BX43" t="s">
-        <v>451</v>
-      </c>
-      <c r="BY43" t="s">
-        <v>455</v>
-      </c>
-      <c r="BZ43">
-        <v>2026</v>
-      </c>
-      <c r="CA43">
-        <v>50</v>
-      </c>
-      <c r="CB43" t="s">
-        <v>472</v>
-      </c>
-      <c r="CC43" t="s">
-        <v>494</v>
-      </c>
-      <c r="CD43" t="s">
-        <v>510</v>
-      </c>
-      <c r="CE43" t="s">
-        <v>517</v>
-      </c>
-      <c r="DE43" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="44" spans="1:109">
-      <c r="A44">
-        <v>1385414</v>
-      </c>
-      <c r="B44" t="s">
-        <v>129</v>
-      </c>
-      <c r="C44" t="s">
-        <v>154</v>
-      </c>
-      <c r="D44" t="s">
-        <v>182</v>
-      </c>
-      <c r="E44" t="s">
-        <v>194</v>
-      </c>
-      <c r="F44">
-        <v>543442305585</v>
-      </c>
-      <c r="G44" t="s">
-        <v>196</v>
-      </c>
-      <c r="H44" t="s">
-        <v>198</v>
-      </c>
-      <c r="I44">
-        <v>9</v>
-      </c>
-      <c r="J44" t="s">
-        <v>225</v>
-      </c>
-      <c r="K44">
-        <v>69</v>
-      </c>
-      <c r="L44" t="s">
-        <v>233</v>
-      </c>
-      <c r="M44">
-        <v>103</v>
-      </c>
-      <c r="N44" t="s">
-        <v>238</v>
-      </c>
-      <c r="O44" t="s">
-        <v>243</v>
-      </c>
-      <c r="P44" t="s">
-        <v>249</v>
-      </c>
-      <c r="T44" t="s">
-        <v>257</v>
-      </c>
-      <c r="U44" t="s">
-        <v>261</v>
-      </c>
-      <c r="V44" t="s">
-        <v>292</v>
-      </c>
-      <c r="W44" t="s">
-        <v>294</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>298</v>
-      </c>
-      <c r="AA44" t="s">
-        <v>182</v>
-      </c>
-      <c r="BB44">
-        <v>1</v>
-      </c>
-      <c r="BC44" t="s">
-        <v>226</v>
-      </c>
-      <c r="BD44">
-        <v>24</v>
-      </c>
-      <c r="BE44" t="s">
-        <v>323</v>
-      </c>
-      <c r="BF44">
-        <v>1050</v>
-      </c>
-      <c r="BG44" t="s">
-        <v>333</v>
-      </c>
-      <c r="BH44">
-        <v>1</v>
-      </c>
-      <c r="BI44" t="s">
-        <v>344</v>
-      </c>
-      <c r="BJ44" t="s">
-        <v>345</v>
-      </c>
-      <c r="BK44" t="s">
-        <v>346</v>
-      </c>
-      <c r="BL44" t="s">
-        <v>358</v>
-      </c>
-      <c r="BM44" t="s">
-        <v>380</v>
-      </c>
-      <c r="BN44" t="s">
-        <v>392</v>
-      </c>
-      <c r="BO44" t="s">
-        <v>409</v>
-      </c>
-      <c r="BP44" t="s">
-        <v>421</v>
-      </c>
-      <c r="BQ44">
-        <v>1</v>
-      </c>
-      <c r="BV44" t="s">
-        <v>448</v>
-      </c>
-      <c r="BW44">
-        <v>56500</v>
-      </c>
-      <c r="BX44" t="s">
-        <v>451</v>
-      </c>
-      <c r="BY44" t="s">
-        <v>455</v>
-      </c>
-      <c r="BZ44">
-        <v>2026</v>
-      </c>
-      <c r="CA44">
-        <v>50</v>
-      </c>
-      <c r="CB44" t="s">
-        <v>473</v>
-      </c>
-      <c r="CC44" t="s">
-        <v>495</v>
-      </c>
-      <c r="CD44" t="s">
-        <v>511</v>
-      </c>
-      <c r="CE44" t="s">
-        <v>517</v>
-      </c>
-      <c r="DE44" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="45" spans="1:109">
-      <c r="A45">
-        <v>1663213</v>
-      </c>
-      <c r="B45" t="s">
-        <v>130</v>
-      </c>
-      <c r="C45" t="s">
-        <v>155</v>
-      </c>
-      <c r="D45" t="s">
-        <v>183</v>
-      </c>
-      <c r="F45">
-        <v>5493873256079</v>
-      </c>
-      <c r="G45" t="s">
-        <v>195</v>
-      </c>
-      <c r="H45" t="s">
-        <v>198</v>
-      </c>
-      <c r="I45">
-        <v>113</v>
-      </c>
-      <c r="J45" t="s">
-        <v>218</v>
-      </c>
-      <c r="K45">
-        <v>9</v>
-      </c>
-      <c r="L45" t="s">
-        <v>234</v>
-      </c>
-      <c r="M45">
-        <v>297</v>
-      </c>
-      <c r="N45" t="s">
-        <v>235</v>
-      </c>
-      <c r="O45" t="s">
-        <v>244</v>
-      </c>
-      <c r="P45" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>254</v>
-      </c>
-      <c r="R45">
-        <v>551860803098</v>
-      </c>
-      <c r="U45" t="s">
-        <v>261</v>
-      </c>
-      <c r="V45" t="s">
-        <v>293</v>
-      </c>
-      <c r="AA45" t="s">
-        <v>310</v>
-      </c>
-      <c r="AB45" t="s">
-        <v>255</v>
-      </c>
-      <c r="AC45" t="s">
-        <v>319</v>
-      </c>
-      <c r="AD45">
-        <v>0</v>
-      </c>
-      <c r="BB45">
-        <v>3</v>
-      </c>
-      <c r="BC45" t="s">
-        <v>321</v>
-      </c>
-      <c r="BD45">
-        <v>9</v>
-      </c>
-      <c r="BE45" t="s">
-        <v>322</v>
-      </c>
-      <c r="BF45">
-        <v>1716</v>
-      </c>
-      <c r="BG45" t="s">
-        <v>342</v>
-      </c>
-      <c r="BH45">
-        <v>7</v>
-      </c>
-      <c r="BI45" t="s">
-        <v>343</v>
-      </c>
-      <c r="BJ45" t="s">
-        <v>345</v>
-      </c>
-      <c r="BK45" t="s">
-        <v>346</v>
-      </c>
-      <c r="BL45" t="s">
-        <v>359</v>
-      </c>
-      <c r="BM45" t="s">
-        <v>381</v>
-      </c>
-      <c r="BN45" t="s">
-        <v>393</v>
-      </c>
-      <c r="BO45" t="s">
-        <v>394</v>
-      </c>
-      <c r="BP45" t="s">
-        <v>422</v>
-      </c>
-      <c r="BQ45">
-        <v>11</v>
-      </c>
-      <c r="BR45">
-        <v>3</v>
-      </c>
-      <c r="BS45" t="s">
-        <v>424</v>
-      </c>
-      <c r="BT45">
-        <v>2411</v>
-      </c>
-      <c r="BU45" t="s">
-        <v>438</v>
-      </c>
-      <c r="BV45" t="s">
-        <v>439</v>
-      </c>
-      <c r="BW45">
-        <v>75000</v>
-      </c>
-      <c r="BX45" t="s">
-        <v>452</v>
-      </c>
-      <c r="BY45" t="s">
-        <v>454</v>
-      </c>
-      <c r="BZ45">
-        <v>2026</v>
-      </c>
-      <c r="CA45">
-        <v>50</v>
-      </c>
-      <c r="CB45" t="s">
-        <v>474</v>
-      </c>
-      <c r="CC45" t="s">
-        <v>496</v>
-      </c>
-      <c r="CD45" t="s">
-        <v>183</v>
-      </c>
-      <c r="CE45" t="s">
-        <v>517</v>
-      </c>
-      <c r="DE45" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
